--- a/data/satisfaction_detail/2026/1-2月/酒店餐饮客户.xlsx
+++ b/data/satisfaction_detail/2026/1-2月/酒店餐饮客户.xlsx
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>10</v>
